--- a/backend/assets/catalogue/modele_catalogue_fournisseur.xlsx
+++ b/backend/assets/catalogue/modele_catalogue_fournisseur.xlsx
@@ -1,142 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Catalogue" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
-  <si>
-    <t>sku_fournisseur</t>
-  </si>
-  <si>
-    <t>code_ean</t>
-  </si>
-  <si>
-    <t>designation_produit</t>
-  </si>
-  <si>
-    <t>categorie</t>
-  </si>
-  <si>
-    <t>description</t>
-  </si>
-  <si>
-    <t>prix_unitaire_ht</t>
-  </si>
-  <si>
-    <t>taux_tva</t>
-  </si>
-  <si>
-    <t>quantite_stock</t>
-  </si>
-  <si>
-    <t>conditionnement</t>
-  </si>
-  <si>
-    <t>poids_kg</t>
-  </si>
-  <si>
-    <t>url_image</t>
-  </si>
-  <si>
-    <t>KD-MILK-001</t>
-  </si>
-  <si>
-    <t>KD-JUICE-005</t>
-  </si>
-  <si>
-    <t>KD-RICE-012</t>
-  </si>
-  <si>
-    <t>Lait UHT Demi-Écrémé 1L x6</t>
-  </si>
-  <si>
-    <t>Jus d Orange Pur Jus 1L x12</t>
-  </si>
-  <si>
-    <t>Riz Basmati Sac 5kg</t>
-  </si>
-  <si>
-    <t>Alimentaire &gt; Épicerie</t>
-  </si>
-  <si>
-    <t>Boissons &gt; Jus de fruits</t>
-  </si>
-  <si>
-    <t>Lait d origine France enrichi en vitamines</t>
-  </si>
-  <si>
-    <t>Pur jus d orange sans sucres ajoutes</t>
-  </si>
-  <si>
-    <t>Riz blanc basmati longue conservation</t>
-  </si>
-  <si>
-    <t>Carton de 6 briques</t>
-  </si>
-  <si>
-    <t>Carton de 12 bouteilles</t>
-  </si>
-  <si>
-    <t>Sac individuel 5kg</t>
-  </si>
-  <si>
-    <t>https://site.com/images/lait.jpg</t>
-  </si>
-  <si>
-    <t>https://site.com/images/orange.jpg</t>
-  </si>
-  <si>
-    <t>https://site.com/images/riz.jpg</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -144,42 +45,86 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -467,156 +412,201 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>sku_fournisseur</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>code_ean</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>designation_produit</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>categorie</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>prix_unitaire_ht</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>taux_tva</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>quantite_stock</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>conditionnement</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>poids_kg</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>volume_m3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>url_image</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:11">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2">
-        <v>3017620422003</v>
-      </c>
-      <c r="C2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2">
-        <v>5.45</v>
-      </c>
-      <c r="G2">
-        <v>2.1</v>
-      </c>
-      <c r="H2">
-        <v>150</v>
-      </c>
-      <c r="I2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J2">
-        <v>6.2</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>25</v>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>KD-MILK-001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>3017620422003</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Lait UHT Demi-Écrémé 1L x6</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Alimentaire &gt; Épicerie</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Lait d origine France enrichi en vitamines</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>5.45</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Carton de 6 briques</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.007</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://site.com/images/lait.jpg</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:11">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3">
-        <v>3250390001234</v>
-      </c>
-      <c r="C3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3">
-        <v>14.2</v>
-      </c>
-      <c r="G3">
-        <v>2.1</v>
-      </c>
-      <c r="H3">
-        <v>85</v>
-      </c>
-      <c r="I3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J3">
-        <v>12.8</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4">
-        <v>3087941234567</v>
-      </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4">
-        <v>8.9</v>
-      </c>
-      <c r="G4">
-        <v>2.1</v>
-      </c>
-      <c r="H4">
-        <v>300</v>
-      </c>
-      <c r="I4" t="s">
-        <v>24</v>
-      </c>
-      <c r="J4">
-        <v>5</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>27</v>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>KD-JUICE-005</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>3250390001234</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Jus d Orange Pur Jus 1L x12</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Boissons &gt; Jus de fruits</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Pur jus d orange sans sucres ajoutes</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>14.2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Carton de 12 bouteilles</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>12.8</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.014</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://site.com/images/orange.jpg</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="K2" r:id="rId1"/>
-    <hyperlink ref="K3" r:id="rId2"/>
-    <hyperlink ref="K4" r:id="rId3"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>